--- a/samples/DataMappingRegistry-FCC-sample.xlsx
+++ b/samples/DataMappingRegistry-FCC-sample.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Datasets'!A1:I49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">'Attributes'!A1:I482</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Mappings'!A1:J429</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'Flows'!A1:I39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'Flows'!A1:J39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">'Events'!A1:L7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'BusinessTerms'!A1:H63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">'GQL Schema'!A1:I31</definedName>
@@ -55858,17 +55858,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:J39"/>
   <cols>
     <col min="1" max="1" width="21.83203125" customWidth="1"/>
     <col min="2" max="2" width="33.83203125" customWidth="1"/>
     <col min="3" max="3" width="19.83203125" customWidth="1"/>
     <col min="4" max="4" width="19.83203125" customWidth="1"/>
     <col min="5" max="5" width="19.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="19.83203125" customWidth="1"/>
-    <col min="8" max="8" width="37.83203125" customWidth="1"/>
-    <col min="9" max="9" width="19.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" customWidth="1"/>
+    <col min="9" max="9" width="37.83203125" customWidth="1"/>
+    <col min="10" max="10" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -55888,15 +55889,18 @@
         <v>Pattern</v>
       </c>
       <c r="F1" t="str">
+        <v>MappingType</v>
+      </c>
+      <c r="G1" t="str">
         <v>Middleware</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Frequency</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Description</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Status</v>
       </c>
     </row>
@@ -55917,15 +55921,18 @@
         <v>Internal</v>
       </c>
       <c r="F2" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G2" t="str">
         <v>DGS data fetchers</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>On request</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>Entity → GraphQL type.</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -55946,15 +55953,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F3" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G3" t="str">
         <v>Federation 2 composition</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>On request</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>Router fetches product fields for the PDP.</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -55975,15 +55985,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F4" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G4" t="str">
         <v>Apollo Client</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>On request</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>PDP, cart page and placeOrder result → view models.</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56004,15 +56017,18 @@
         <v>Internal</v>
       </c>
       <c r="F5" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G5" t="str">
         <v>React state / Apollo cache</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>On interaction</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>Values carried between pages and forms.</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56033,15 +56049,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F6" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G6" t="str">
         <v>Apollo Client</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>On request</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>addToCart and placeOrder.</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56062,15 +56081,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F7" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G7" t="str">
         <v>Router query plan</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>On request</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>Router plans addToCart / placeOrder onto the commerce subgraph.</v>
       </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56091,15 +56113,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F8" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G8" t="str">
         <v>Federation 2 composition</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>On request</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>cart query and placeOrder result.</v>
       </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56120,15 +56145,18 @@
         <v>Internal</v>
       </c>
       <c r="F9" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G9" t="str">
         <v>TypeORM</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>On request</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>Mutation input / auth context → cart_session and checkout_attempt.</v>
       </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56149,15 +56177,18 @@
         <v>REST API</v>
       </c>
       <c r="F10" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G10" t="str">
         <v>FCC REST client (OAuth2 client credentials, retries, idempotent X-Request-Id)</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>On request</v>
       </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>Create Cart, Add Items, Get Cart. Every call carries the five FCC headers.</v>
       </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56178,15 +56209,18 @@
         <v>REST API</v>
       </c>
       <c r="F11" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G11" t="str">
         <v>FCC REST client</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>On request</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <v>Cart id into cart_session; Get Cart into the cart subgraph and the cart REST API.</v>
       </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56207,15 +56241,18 @@
         <v>REST API</v>
       </c>
       <c r="F12" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G12" t="str">
         <v>FCC REST client</v>
       </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
         <v>On checkout</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
         <v>Initiate Checkout → Initiate Payment → Create Order.</v>
       </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56236,15 +56273,18 @@
         <v>REST API</v>
       </c>
       <c r="F13" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G13" t="str">
         <v>FCC REST client</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <v>On checkout</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <v>Checkout / payment / order ids into checkout_attempt and the placeOrder result.</v>
       </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56265,15 +56305,18 @@
         <v>REST API</v>
       </c>
       <c r="F14" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G14" t="str">
         <v>BFF HTTP client</v>
       </c>
-      <c r="G14" t="str">
+      <c r="H14" t="str">
         <v>On request</v>
       </c>
-      <c r="H14" t="str">
+      <c r="I14" t="str">
         <v>BFF forwards the cart id.</v>
       </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56294,15 +56337,18 @@
         <v>REST API</v>
       </c>
       <c r="F15" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G15" t="str">
         <v>BFF HTTP client</v>
       </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>On request</v>
       </c>
-      <c r="H15" t="str">
+      <c r="I15" t="str">
         <v>BFF shapes the cart screen.</v>
       </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56323,15 +56369,18 @@
         <v>REST API</v>
       </c>
       <c r="F16" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G16" t="str">
         <v>fetch</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
         <v>On request</v>
       </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
       <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56352,15 +56401,18 @@
         <v>REST API</v>
       </c>
       <c r="F17" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G17" t="str">
         <v>HTTPS webhook, HMAC-signed</v>
       </c>
-      <c r="G17" t="str">
+      <c r="H17" t="str">
         <v>On payment termination</v>
       </c>
-      <c r="H17" t="str">
+      <c r="I17" t="str">
         <v>FCC notifies external systems at payment termination; the bridge acknowledges with 202 and processes asynchronously.</v>
       </c>
-      <c r="I17" t="str">
+      <c r="J17" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56381,15 +56433,18 @@
         <v>REST API</v>
       </c>
       <c r="F18" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G18" t="str">
         <v>FCC REST client</v>
       </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>Per webhook</v>
       </c>
-      <c r="H18" t="str">
+      <c r="I18" t="str">
         <v>Reads the full checkout for the notified checkoutId.</v>
       </c>
-      <c r="I18" t="str">
+      <c r="J18" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56410,15 +56465,18 @@
         <v>REST API</v>
       </c>
       <c r="F19" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G19" t="str">
         <v>FCC REST client → Kafka producer</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
         <v>Per webhook</v>
       </c>
-      <c r="H19" t="str">
+      <c r="I19" t="str">
         <v>Maps the FCC checkout into the canonical order event.</v>
       </c>
-      <c r="I19" t="str">
+      <c r="J19" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56439,15 +56497,18 @@
         <v>Internal</v>
       </c>
       <c r="F20" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G20" t="str">
         <v>Spring</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <v>Per webhook</v>
       </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
       <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56468,15 +56529,18 @@
         <v>Kafka event</v>
       </c>
       <c r="F21" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G21" t="str">
         <v>Spring Kafka consumer</v>
       </c>
-      <c r="G21" t="str">
+      <c r="H21" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H21" t="str">
+      <c r="I21" t="str">
         <v>Order Service upserts the order and its lines.</v>
       </c>
-      <c r="I21" t="str">
+      <c r="J21" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56497,15 +56561,18 @@
         <v>CDC</v>
       </c>
       <c r="F22" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G22" t="str">
         <v>Kafka Connect JDBC source + SMTs</v>
       </c>
-      <c r="G22" t="str">
+      <c r="H22" t="str">
         <v>Near real-time</v>
       </c>
-      <c r="H22" t="str">
+      <c r="I22" t="str">
         <v>Change data capture on C_B_PRODUCT.</v>
       </c>
-      <c r="I22" t="str">
+      <c r="J22" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -56526,15 +56593,18 @@
         <v>Kafka event</v>
       </c>
       <c r="F23" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G23" t="str">
         <v>Databricks Structured Streaming (Kafka source)</v>
       </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <v>Streaming</v>
       </c>
-      <c r="H23" t="str">
+      <c r="I23" t="str">
         <v>Bronze stream of golden-record changes, merged into silver.</v>
       </c>
-      <c r="I23" t="str">
+      <c r="J23" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56555,15 +56625,18 @@
         <v>File (CSV)</v>
       </c>
       <c r="F24" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G24" t="str">
         <v>Databricks Auto Loader (JSONL on S3)</v>
       </c>
-      <c r="G24" t="str">
+      <c r="H24" t="str">
         <v>Daily 02:00</v>
       </c>
-      <c r="H24" t="str">
+      <c r="I24" t="str">
         <v>Daily JSONL export joined to the MDM record by SKU.</v>
       </c>
-      <c r="I24" t="str">
+      <c r="J24" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56584,15 +56657,18 @@
         <v>Internal</v>
       </c>
       <c r="F25" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G25" t="str">
         <v>Databricks jobs / Delta Live Tables</v>
       </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
         <v>Every 15 min</v>
       </c>
-      <c r="H25" t="str">
+      <c r="I25" t="str">
         <v>Curates silver into gold and writes the outbound event, file and feed-log records.</v>
       </c>
-      <c r="I25" t="str">
+      <c r="J25" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56613,15 +56689,18 @@
         <v>Kafka event</v>
       </c>
       <c r="F26" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G26" t="str">
         <v>Spring Kafka consumer</v>
       </c>
-      <c r="G26" t="str">
+      <c r="H26" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H26" t="str">
+      <c r="I26" t="str">
         <v>Product Service upserts the published catalog.</v>
       </c>
-      <c r="I26" t="str">
+      <c r="J26" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56642,15 +56721,18 @@
         <v>REST API</v>
       </c>
       <c r="F27" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G27" t="str">
         <v>Databricks job + FCC REST client</v>
       </c>
-      <c r="G27" t="str">
+      <c r="H27" t="str">
         <v>Every 15 min</v>
       </c>
-      <c r="H27" t="str">
+      <c r="I27" t="str">
         <v>Batch upsert of changed gold rows.</v>
       </c>
-      <c r="I27" t="str">
+      <c r="J27" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56671,15 +56753,18 @@
         <v>REST API</v>
       </c>
       <c r="F28" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G28" t="str">
         <v>FCC REST client</v>
       </c>
-      <c r="G28" t="str">
+      <c r="H28" t="str">
         <v>Every 15 min</v>
       </c>
-      <c r="H28" t="str">
+      <c r="I28" t="str">
         <v>Listing ids per SKU and the feed id.</v>
       </c>
-      <c r="I28" t="str">
+      <c r="J28" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56700,15 +56785,18 @@
         <v>REST API</v>
       </c>
       <c r="F29" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G29" t="str">
         <v>HTTPS webhook, HMAC-signed</v>
       </c>
-      <c r="G29" t="str">
+      <c r="H29" t="str">
         <v>Per feed</v>
       </c>
-      <c r="H29" t="str">
+      <c r="I29" t="str">
         <v>FCC reports the final status of a feed.</v>
       </c>
-      <c r="I29" t="str">
+      <c r="J29" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56729,15 +56817,18 @@
         <v>REST API</v>
       </c>
       <c r="F30" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G30" t="str">
         <v>Algolia API client (batch)</v>
       </c>
-      <c r="G30" t="str">
+      <c r="H30" t="str">
         <v>Every 15 min</v>
       </c>
-      <c r="H30" t="str">
+      <c r="I30" t="str">
         <v>Batch updateObject / deleteObject on prod_products.</v>
       </c>
-      <c r="I30" t="str">
+      <c r="J30" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56758,15 +56849,18 @@
         <v>REST API</v>
       </c>
       <c r="F31" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G31" t="str">
         <v>Algolia API client</v>
       </c>
-      <c r="G31" t="str">
+      <c r="H31" t="str">
         <v>Every 15 min</v>
       </c>
-      <c r="H31" t="str">
+      <c r="I31" t="str">
         <v>taskID kept on the feed run.</v>
       </c>
-      <c r="I31" t="str">
+      <c r="J31" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56787,15 +56881,18 @@
         <v>File (CSV)</v>
       </c>
       <c r="F32" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G32" t="str">
         <v>S3 + Elasticsearch _bulk loader</v>
       </c>
-      <c r="G32" t="str">
+      <c r="H32" t="str">
         <v>Hourly</v>
       </c>
-      <c r="H32" t="str">
+      <c r="I32" t="str">
         <v>NDJSON bulk file loaded into the products index.</v>
       </c>
-      <c r="I32" t="str">
+      <c r="J32" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56816,15 +56913,18 @@
         <v>Internal</v>
       </c>
       <c r="F33" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G33" t="str">
         <v>Transactional outbox</v>
       </c>
-      <c r="G33" t="str">
+      <c r="H33" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H33" t="str">
-        <v/>
-      </c>
       <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56845,15 +56945,18 @@
         <v>Internal</v>
       </c>
       <c r="F34" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G34" t="str">
         <v>Bulk loader</v>
       </c>
-      <c r="G34" t="str">
+      <c r="H34" t="str">
         <v>Per file</v>
       </c>
-      <c r="H34" t="str">
-        <v/>
-      </c>
       <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56874,15 +56977,18 @@
         <v>Kafka event</v>
       </c>
       <c r="F35" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G35" t="str">
         <v>ClickHouse Kafka engine + materialized view</v>
       </c>
-      <c r="G35" t="str">
+      <c r="H35" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H35" t="str">
+      <c r="I35" t="str">
         <v>Core feed volume and freshness.</v>
       </c>
-      <c r="I35" t="str">
+      <c r="J35" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56903,15 +57009,18 @@
         <v>Kafka event</v>
       </c>
       <c r="F36" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G36" t="str">
         <v>ClickHouse Kafka engine + materialized view</v>
       </c>
-      <c r="G36" t="str">
+      <c r="H36" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H36" t="str">
-        <v/>
-      </c>
       <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56932,15 +57041,18 @@
         <v>Kafka event</v>
       </c>
       <c r="F37" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G37" t="str">
         <v>ClickHouse Kafka engine + materialized view</v>
       </c>
-      <c r="G37" t="str">
+      <c r="H37" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H37" t="str">
-        <v/>
-      </c>
       <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56961,15 +57073,18 @@
         <v>Kafka event</v>
       </c>
       <c r="F38" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G38" t="str">
         <v>ClickHouse Kafka engine + materialized view</v>
       </c>
-      <c r="G38" t="str">
+      <c r="H38" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H38" t="str">
-        <v/>
-      </c>
       <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -56990,21 +57105,24 @@
         <v>Internal</v>
       </c>
       <c r="F39" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G39" t="str">
         <v>ClickHouse materialized view</v>
       </c>
-      <c r="G39" t="str">
+      <c r="H39" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H39" t="str">
-        <v/>
-      </c>
       <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
         <v>Proposed</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I39"/>
-  <dataValidations count="4">
+  <autoFilter ref="A1:J39"/>
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="C2:C1000">
       <formula1>Applications!$A$2:$A$1000</formula1>
     </dataValidation>
@@ -57014,12 +57132,15 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="E2:E1000">
       <formula1>"REST API,GraphQL,Kafka event,File (CSV),CDC,Internal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="I2:I1000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="F2:F1000">
+      <formula1>"API data mapping,Domain data mapping"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="J2:J1000">
       <formula1>"Draft,Proposed,Approved,Deprecated"</formula1>
     </dataValidation>
   </dataValidations>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J39"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -59067,7 +59188,7 @@
         <v>Flows</v>
       </c>
       <c r="B8" t="str">
-        <v>Integration flows between two applications with their pattern: REST API, GraphQL, Kafka event, File (CSV), CDC, or Internal (inside one application).</v>
+        <v>Integration flows between two applications with their pattern: REST API, GraphQL, Kafka event, File (CSV), CDC, or Internal (inside one application). MappingType: API data mapping = a call from the front end to the back end (front end → BFF / FedGQL router → domain / integration service → database or third party); Domain data mapping = a data sync (core → data hub → data platform, and the hub's subscribers). Left empty, it is filled in from the applications and pattern.</v>
       </c>
     </row>
     <row r="9">
